--- a/data/HPC_Question_Bank_Template.xlsx
+++ b/data/HPC_Question_Bank_Template.xlsx
@@ -1815,16 +1815,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Customer Experience</t>
+          <t>APD - Airport Delivery</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1888,16 +1888,8 @@
       <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Head of CX</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Front-line</t>
-        </is>
-      </c>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1907,12 +1899,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>ASD - Airport Service Delivery</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1923,16 +1915,8 @@
       <c r="E3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CCO</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1942,12 +1926,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>BIM - Brand, Insights &amp; Marketing Communications</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Corporate</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1958,16 +1942,8 @@
       <c r="E4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Ground + inflight</t>
-        </is>
-      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1977,7 +1953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>CAF - Corporate Affairs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1993,16 +1969,8 @@
       <c r="E5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CIO</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2012,7 +1980,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>People &amp; Culture</t>
+          <t>CAY - Cathay Academy</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2028,16 +1996,8 @@
       <c r="E6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>CPO</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2047,7 +2007,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>CCD - Customer Care</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2063,16 +2023,8 @@
       <c r="E7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>CFO</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2082,7 +2034,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>CED - Customer Experience Design</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2098,16 +2050,8 @@
       <c r="E8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Head of Cargo</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Freight</t>
-        </is>
-      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2117,12 +2061,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cathay Academy</t>
+          <t>CGO - Cargo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Corporate</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2133,18 +2077,717 @@
       <c r="E9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Head of Academy</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CRR - Customer Relationship &amp; Retail</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>DEX - Digital Experience</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>DGT - Digital</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ENG - Engineering</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>FIN - Finance</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>FOP - Flight Operations</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>GBS - Global Business Service</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>GIA - Group Internal Audit</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>GLC - Group Legal &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>GMD - Group Medical</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>GOR - Group Opportunities and Risks</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>GSR - Group Safety and Operational Risk Management</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>GSD - Group Sustainability</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>IMT - Information Technology</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>IOC - Integrated Operations</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ISD - Inflight Service Delivery</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>LDC - Logistics and Distribution Centre</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>PLN - Planning</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>D27</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>PPL - People - Employee Experience</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>D28</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>PSD - Property and Service</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>PVO - Procurement &amp; Aircraft Trading</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>D30</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>REV - Revenue Management</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>D31</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>SND - Sales &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>D32</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>OPN - Operations</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>D33</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>SUB - Subsidiaries</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>EXO - Executive Team</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Active,Inactive"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2194,7 +2837,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2613,7 +3256,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Baseline v3.0 (PACE)</t>
+          <t>Baseline v3.1 — 34 departments</t>
         </is>
       </c>
       <c r="F2" s="4" t="n"/>

--- a/data/HPC_Question_Bank_Template.xlsx
+++ b/data/HPC_Question_Bank_Template.xlsx
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Dysfunc upper.</t>
+          <t>At-Risk upper.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Balanced upper.</t>
+          <t>Developing upper.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Baseline v3.1 — 34 departments</t>
+          <t>Baseline v3.3 — 34 depts, broad spectrum</t>
         </is>
       </c>
       <c r="F2" s="4" t="n"/>

--- a/data/HPC_Question_Bank_Template.xlsx
+++ b/data/HPC_Question_Bank_Template.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Powered by Cathay Academy. Elements: Purpose · Alliance · Collaboration · Excellence.</t>
+          <t>Powered by Cathay Academy. Elements: Purpose · Alliance · Coordination · Excellence.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>I understand how my role contributes to the organization's overall mission.</t>
+          <t>I understand how my role contributes to the organisation's overall mission.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>My daily work is meaningfully aligned with the organization's strategic objectives.</t>
+          <t>My daily work is meaningfully aligned with the organisation's strategic objectives.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Our leaders demonstrate the behaviors expected of a high-performing culture.</t>
+          <t>Our leaders demonstrate the behaviours expected of a high-performing culture.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Relationships within our team are characterized by mutual respect and trust.</t>
+          <t>Relationships within our team are characterised by mutual respect and trust.</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>A growth mindset is actively encouraged and modeled in our team.</t>
+          <t>A growth mindset is actively encouraged and modelled in our team.</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>We celebrate achievements and recognize high performance in meaningful ways.</t>
+          <t>We celebrate achievements and recognise high performance in meaningful ways.</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <formula1>"Active,Inactive"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Purpose,Alliance,Collaboration,Excellence"</formula1>
+      <formula1>"Purpose,Alliance,Coordination,Excellence"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Purpose · Alliance · Collaboration · Excellence.</t>
+          <t>Purpose · Alliance · Coordination · Excellence.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3236,7 +3236,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Initial</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Framework + spelling</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Baseline v3.3 — 34 depts, broad spectrum</t>
+          <t>v3.4 — element renamed Collaboration -&gt; Coordination; British English spelling</t>
         </is>
       </c>
       <c r="F2" s="4" t="n"/>
